--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23520" windowHeight="11670"/>
+    <workbookView windowWidth="24240" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -218,7 +218,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,13 +231,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -715,133 +708,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -851,8 +844,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1898,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24240" windowHeight="11775"/>
+    <workbookView windowWidth="16920" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
     <t>弓箭手</t>
   </si>
   <si>
-    <t>子弹所有Unit</t>
+    <t>子弹Unit</t>
   </si>
   <si>
     <t>子弹</t>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16920" windowHeight="12360"/>
+    <workbookView windowWidth="24720" windowHeight="9705"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J16" s="1">
         <v>6000</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J17" s="1">
         <v>6000</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>子弹</t>
+  </si>
+  <si>
+    <t>机器人</t>
+  </si>
+  <si>
+    <t>机器人测试</t>
   </si>
   <si>
     <t>怪物测试1</t>
@@ -1197,7 +1203,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:S17"/>
+  <dimension ref="B1:S18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1926,16 +1932,16 @@
     </row>
     <row r="16" spans="2:19">
       <c r="C16" s="1">
-        <v>10001</v>
+        <v>9101</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>55</v>
@@ -1950,36 +1956,36 @@
         <v>6000</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L16" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M16" s="1">
         <v>1</v>
       </c>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S16" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="C17" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
@@ -2027,6 +2033,59 @@
         <v>6</v>
       </c>
       <c r="S17" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19">
+      <c r="C18" s="1">
+        <v>10002</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J18" s="1">
+        <v>6000</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>6</v>
+      </c>
+      <c r="S18" s="1">
         <v>30</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24720" windowHeight="9705"/>
+    <workbookView windowWidth="22500" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -166,25 +166,46 @@
     <t>带有强力攻击技能4</t>
   </si>
   <si>
-    <t>角色数值模板</t>
-  </si>
-  <si>
-    <t>通用模板</t>
-  </si>
-  <si>
-    <t>郭晓华</t>
+    <t>骑士数值模板</t>
+  </si>
+  <si>
+    <t>骑士Unit</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>法师数值模板</t>
+  </si>
+  <si>
+    <t>法师Unit</t>
   </si>
   <si>
     <t>法师</t>
   </si>
   <si>
-    <t>西纱</t>
+    <t>盗贼数值模板</t>
+  </si>
+  <si>
+    <t>盗贼Unit</t>
   </si>
   <si>
     <t>盗贼</t>
   </si>
   <si>
+    <t>牧师数值模板</t>
+  </si>
+  <si>
+    <t>牧师Unit</t>
+  </si>
+  <si>
     <t>牧师</t>
+  </si>
+  <si>
+    <t>弓箭手数值模板</t>
+  </si>
+  <si>
+    <t>弓箭手Unit</t>
   </si>
   <si>
     <t>弓箭手</t>
@@ -1626,7 +1647,7 @@
         <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
@@ -1673,13 +1694,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1726,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1">
         <v>3</v>
@@ -1779,13 +1800,13 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H13" s="1">
         <v>4</v>
@@ -1832,13 +1853,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H14" s="1">
         <v>5</v>
@@ -1885,13 +1906,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1938,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1991,13 +2012,13 @@
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -2044,13 +2065,13 @@
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
